--- a/MARLIN V2/Tenkara/4 - Subteams/TCA/Development/Sizing_script/designs.xlsx
+++ b/MARLIN V2/Tenkara/4 - Subteams/TCA/Development/Sizing_script/designs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N291"/>
+  <dimension ref="A1:O291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,11 @@
           <t>T_chamber_K</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>sigma_vM_MPa</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -531,6 +536,9 @@
       <c r="N2" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O2" t="n">
+        <v>6.932089065677268</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -575,6 +583,9 @@
       <c r="N3" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O3" t="n">
+        <v>8.830351998109592</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -619,6 +630,9 @@
       <c r="N4" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O4" t="n">
+        <v>6.932089065677268</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -663,6 +677,9 @@
       <c r="N5" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O5" t="n">
+        <v>8.830351998109592</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -707,6 +724,9 @@
       <c r="N6" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O6" t="n">
+        <v>6.932089065677268</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -751,6 +771,9 @@
       <c r="N7" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O7" t="n">
+        <v>11.67774639675808</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -795,6 +818,9 @@
       <c r="N8" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O8" t="n">
+        <v>8.830351998109592</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -839,6 +865,9 @@
       <c r="N9" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O9" t="n">
+        <v>6.932089065677268</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -883,6 +912,9 @@
       <c r="N10" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O10" t="n">
+        <v>16.42340372783888</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -927,6 +959,9 @@
       <c r="N11" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O11" t="n">
+        <v>11.67774639675808</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -971,6 +1006,9 @@
       <c r="N12" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O12" t="n">
+        <v>8.830351998109592</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1015,6 +1053,9 @@
       <c r="N13" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O13" t="n">
+        <v>6.932089065677268</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1059,6 +1100,9 @@
       <c r="N14" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O14" t="n">
+        <v>16.42340372783888</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1103,6 +1147,9 @@
       <c r="N15" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O15" t="n">
+        <v>11.67774639675808</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1147,6 +1194,9 @@
       <c r="N16" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O16" t="n">
+        <v>8.830351998109592</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1191,6 +1241,9 @@
       <c r="N17" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O17" t="n">
+        <v>6.932089065677268</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1235,6 +1288,9 @@
       <c r="N18" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O18" t="n">
+        <v>7.252620223370283</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1279,6 +1335,9 @@
       <c r="N19" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O19" t="n">
+        <v>16.42340372783888</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1323,6 +1382,9 @@
       <c r="N20" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O20" t="n">
+        <v>11.67774639675808</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1367,6 +1429,9 @@
       <c r="N21" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O21" t="n">
+        <v>8.830351998109592</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1411,6 +1476,9 @@
       <c r="N22" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O22" t="n">
+        <v>6.932089065677268</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1455,6 +1523,9 @@
       <c r="N23" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O23" t="n">
+        <v>7.252620223370283</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1499,6 +1570,9 @@
       <c r="N24" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O24" t="n">
+        <v>16.42340372783888</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1543,6 +1617,9 @@
       <c r="N25" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O25" t="n">
+        <v>11.67774639675808</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1587,6 +1664,9 @@
       <c r="N26" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O26" t="n">
+        <v>8.830351998109592</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1631,6 +1711,9 @@
       <c r="N27" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O27" t="n">
+        <v>6.932089065677268</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1675,6 +1758,9 @@
       <c r="N28" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O28" t="n">
+        <v>9.234924631541917</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1719,6 +1805,9 @@
       <c r="N29" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O29" t="n">
+        <v>7.252620223370283</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1763,6 +1852,9 @@
       <c r="N30" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O30" t="n">
+        <v>16.42340372783888</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1807,6 +1899,9 @@
       <c r="N31" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O31" t="n">
+        <v>11.67774639675808</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1851,6 +1946,9 @@
       <c r="N32" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O32" t="n">
+        <v>8.830351998109592</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1895,6 +1993,9 @@
       <c r="N33" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O33" t="n">
+        <v>6.932089065677268</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1939,6 +2040,9 @@
       <c r="N34" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O34" t="n">
+        <v>9.234924631541917</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1983,6 +2087,9 @@
       <c r="N35" t="n">
         <v>3263.939951911218</v>
       </c>
+      <c r="O35" t="n">
+        <v>7.252620223370283</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2027,6 +2134,9 @@
       <c r="N36" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O36" t="n">
+        <v>7.278693518961131</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2071,6 +2181,9 @@
       <c r="N37" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O37" t="n">
+        <v>9.271869598015069</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2115,6 +2228,9 @@
       <c r="N38" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O38" t="n">
+        <v>7.278693518961131</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2159,6 +2275,9 @@
       <c r="N39" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O39" t="n">
+        <v>9.271869598015069</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2203,6 +2322,9 @@
       <c r="N40" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O40" t="n">
+        <v>7.278693518961131</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2247,6 +2369,9 @@
       <c r="N41" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O41" t="n">
+        <v>12.26163371659598</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2291,6 +2416,9 @@
       <c r="N42" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O42" t="n">
+        <v>9.271869598015069</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2335,6 +2463,9 @@
       <c r="N43" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O43" t="n">
+        <v>7.278693518961131</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2379,6 +2510,9 @@
       <c r="N44" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O44" t="n">
+        <v>17.24457391423083</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2423,6 +2557,9 @@
       <c r="N45" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O45" t="n">
+        <v>12.26163371659598</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2467,6 +2604,9 @@
       <c r="N46" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O46" t="n">
+        <v>9.271869598015069</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2511,6 +2651,9 @@
       <c r="N47" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O47" t="n">
+        <v>7.278693518961131</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2555,6 +2698,9 @@
       <c r="N48" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O48" t="n">
+        <v>17.24457391423083</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2599,6 +2745,9 @@
       <c r="N49" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O49" t="n">
+        <v>12.26163371659598</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2643,6 +2792,9 @@
       <c r="N50" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O50" t="n">
+        <v>9.271869598015069</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2687,6 +2839,9 @@
       <c r="N51" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O51" t="n">
+        <v>7.278693518961131</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2731,6 +2886,9 @@
       <c r="N52" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O52" t="n">
+        <v>7.615251234538795</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2775,6 +2933,9 @@
       <c r="N53" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O53" t="n">
+        <v>17.24457391423083</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2819,6 +2980,9 @@
       <c r="N54" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O54" t="n">
+        <v>12.26163371659598</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2863,6 +3027,9 @@
       <c r="N55" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O55" t="n">
+        <v>9.271869598015069</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2907,6 +3074,9 @@
       <c r="N56" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O56" t="n">
+        <v>7.278693518961131</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2951,6 +3121,9 @@
       <c r="N57" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O57" t="n">
+        <v>7.615251234538795</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2995,6 +3168,9 @@
       <c r="N58" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O58" t="n">
+        <v>17.24457391423083</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3039,6 +3215,9 @@
       <c r="N59" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O59" t="n">
+        <v>12.26163371659598</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3083,6 +3262,9 @@
       <c r="N60" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O60" t="n">
+        <v>9.271869598015069</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3127,6 +3309,9 @@
       <c r="N61" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O61" t="n">
+        <v>7.278693518961131</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3171,6 +3356,9 @@
       <c r="N62" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O62" t="n">
+        <v>9.696670863119015</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3215,6 +3403,9 @@
       <c r="N63" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O63" t="n">
+        <v>7.615251234538795</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3259,6 +3450,9 @@
       <c r="N64" t="n">
         <v>3268.411760496761</v>
       </c>
+      <c r="O64" t="n">
+        <v>7.278693518961131</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3303,6 +3497,9 @@
       <c r="N65" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O65" t="n">
+        <v>7.625297972244995</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3347,6 +3544,9 @@
       <c r="N66" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O66" t="n">
+        <v>7.625297972244995</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3391,6 +3591,9 @@
       <c r="N67" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O67" t="n">
+        <v>9.713387197920548</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3435,6 +3638,9 @@
       <c r="N68" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O68" t="n">
+        <v>7.625297972244995</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3479,6 +3685,9 @@
       <c r="N69" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O69" t="n">
+        <v>12.84552103643388</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3523,6 +3732,9 @@
       <c r="N70" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O70" t="n">
+        <v>9.713387197920548</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3567,6 +3779,9 @@
       <c r="N71" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O71" t="n">
+        <v>7.625297972244995</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3611,6 +3826,9 @@
       <c r="N72" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O72" t="n">
+        <v>12.84552103643388</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3655,6 +3873,9 @@
       <c r="N73" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O73" t="n">
+        <v>9.713387197920548</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3699,6 +3920,9 @@
       <c r="N74" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O74" t="n">
+        <v>7.625297972244995</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3743,6 +3967,9 @@
       <c r="N75" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O75" t="n">
+        <v>18.06574410062277</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3787,6 +4014,9 @@
       <c r="N76" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O76" t="n">
+        <v>12.84552103643388</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3831,6 +4061,9 @@
       <c r="N77" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O77" t="n">
+        <v>9.713387197920548</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3875,6 +4108,9 @@
       <c r="N78" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O78" t="n">
+        <v>7.625297972244995</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3919,6 +4155,9 @@
       <c r="N79" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O79" t="n">
+        <v>18.06574410062277</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3963,6 +4202,9 @@
       <c r="N80" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O80" t="n">
+        <v>12.84552103643388</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4007,6 +4249,9 @@
       <c r="N81" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O81" t="n">
+        <v>9.713387197920548</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4051,6 +4296,9 @@
       <c r="N82" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O82" t="n">
+        <v>7.625297972244995</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4095,6 +4343,9 @@
       <c r="N83" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O83" t="n">
+        <v>7.977882245707311</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4139,6 +4390,9 @@
       <c r="N84" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O84" t="n">
+        <v>18.06574410062277</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4183,6 +4437,9 @@
       <c r="N85" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O85" t="n">
+        <v>12.84552103643388</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4227,6 +4484,9 @@
       <c r="N86" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O86" t="n">
+        <v>9.713387197920548</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4271,6 +4531,9 @@
       <c r="N87" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O87" t="n">
+        <v>7.625297972244995</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4315,6 +4578,9 @@
       <c r="N88" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O88" t="n">
+        <v>7.977882245707311</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4359,6 +4625,9 @@
       <c r="N89" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O89" t="n">
+        <v>9.713387197920548</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4403,6 +4672,9 @@
       <c r="N90" t="n">
         <v>3272.655789072595</v>
       </c>
+      <c r="O90" t="n">
+        <v>7.625297972244995</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4447,6 +4719,9 @@
       <c r="N91" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O91" t="n">
+        <v>7.97190242552886</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4491,6 +4766,9 @@
       <c r="N92" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O92" t="n">
+        <v>10.15490479782603</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4535,6 +4813,9 @@
       <c r="N93" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O93" t="n">
+        <v>7.97190242552886</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4579,6 +4860,9 @@
       <c r="N94" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O94" t="n">
+        <v>10.15490479782603</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4623,6 +4907,9 @@
       <c r="N95" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O95" t="n">
+        <v>7.97190242552886</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4667,6 +4954,9 @@
       <c r="N96" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O96" t="n">
+        <v>13.42940835627179</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4711,6 +5001,9 @@
       <c r="N97" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O97" t="n">
+        <v>10.15490479782603</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4755,6 +5048,9 @@
       <c r="N98" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O98" t="n">
+        <v>7.97190242552886</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4799,6 +5095,9 @@
       <c r="N99" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O99" t="n">
+        <v>13.42940835627179</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4843,6 +5142,9 @@
       <c r="N100" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O100" t="n">
+        <v>10.15490479782603</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4887,6 +5189,9 @@
       <c r="N101" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O101" t="n">
+        <v>7.97190242552886</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4931,6 +5236,9 @@
       <c r="N102" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O102" t="n">
+        <v>18.88691428701472</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4975,6 +5283,9 @@
       <c r="N103" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O103" t="n">
+        <v>13.42940835627179</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5019,6 +5330,9 @@
       <c r="N104" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O104" t="n">
+        <v>10.15490479782603</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5063,6 +5377,9 @@
       <c r="N105" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O105" t="n">
+        <v>7.97190242552886</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5107,6 +5424,9 @@
       <c r="N106" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O106" t="n">
+        <v>18.88691428701472</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5151,6 +5471,9 @@
       <c r="N107" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O107" t="n">
+        <v>13.42940835627179</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5195,6 +5518,9 @@
       <c r="N108" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O108" t="n">
+        <v>10.15490479782603</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5239,6 +5565,9 @@
       <c r="N109" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O109" t="n">
+        <v>7.97190242552886</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5283,6 +5612,9 @@
       <c r="N110" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O110" t="n">
+        <v>8.340513256875825</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5327,6 +5659,9 @@
       <c r="N111" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O111" t="n">
+        <v>18.88691428701472</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5371,6 +5706,9 @@
       <c r="N112" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O112" t="n">
+        <v>13.42940835627179</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5415,6 +5753,9 @@
       <c r="N113" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O113" t="n">
+        <v>10.15490479782603</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5459,6 +5800,9 @@
       <c r="N114" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O114" t="n">
+        <v>7.97190242552886</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5503,6 +5847,9 @@
       <c r="N115" t="n">
         <v>3276.692811655986</v>
       </c>
+      <c r="O115" t="n">
+        <v>8.340513256875825</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5547,6 +5894,9 @@
       <c r="N116" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O116" t="n">
+        <v>8.318506878812723</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5591,6 +5941,9 @@
       <c r="N117" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O117" t="n">
+        <v>8.318506878812723</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5635,6 +5988,9 @@
       <c r="N118" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O118" t="n">
+        <v>10.59642239773151</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5679,6 +6035,9 @@
       <c r="N119" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O119" t="n">
+        <v>8.318506878812723</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5723,6 +6082,9 @@
       <c r="N120" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O120" t="n">
+        <v>10.59642239773151</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5767,6 +6129,9 @@
       <c r="N121" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O121" t="n">
+        <v>8.318506878812723</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5811,6 +6176,9 @@
       <c r="N122" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O122" t="n">
+        <v>14.01329567610969</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5855,6 +6223,9 @@
       <c r="N123" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O123" t="n">
+        <v>10.59642239773151</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5899,6 +6270,9 @@
       <c r="N124" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O124" t="n">
+        <v>8.318506878812723</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5943,6 +6317,9 @@
       <c r="N125" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O125" t="n">
+        <v>14.01329567610969</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5987,6 +6364,9 @@
       <c r="N126" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O126" t="n">
+        <v>10.59642239773151</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -6031,6 +6411,9 @@
       <c r="N127" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O127" t="n">
+        <v>8.318506878812723</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -6075,6 +6458,9 @@
       <c r="N128" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O128" t="n">
+        <v>19.70808447340666</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6119,6 +6505,9 @@
       <c r="N129" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O129" t="n">
+        <v>14.01329567610969</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -6163,6 +6552,9 @@
       <c r="N130" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O130" t="n">
+        <v>10.59642239773151</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -6207,6 +6599,9 @@
       <c r="N131" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O131" t="n">
+        <v>8.318506878812723</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -6251,6 +6646,9 @@
       <c r="N132" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O132" t="n">
+        <v>8.703144268044339</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -6295,6 +6693,9 @@
       <c r="N133" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O133" t="n">
+        <v>19.70808447340666</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -6339,6 +6740,9 @@
       <c r="N134" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O134" t="n">
+        <v>14.01329567610969</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -6383,6 +6787,9 @@
       <c r="N135" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O135" t="n">
+        <v>10.59642239773151</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -6427,6 +6834,9 @@
       <c r="N136" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O136" t="n">
+        <v>8.318506878812723</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -6471,6 +6881,9 @@
       <c r="N137" t="n">
         <v>3280.540899665024</v>
       </c>
+      <c r="O137" t="n">
+        <v>8.703144268044339</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6515,6 +6928,9 @@
       <c r="N138" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O138" t="n">
+        <v>8.665111332096586</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -6559,6 +6975,9 @@
       <c r="N139" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O139" t="n">
+        <v>8.665111332096586</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -6603,6 +7022,9 @@
       <c r="N140" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O140" t="n">
+        <v>11.03793999763699</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -6647,6 +7069,9 @@
       <c r="N141" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O141" t="n">
+        <v>8.665111332096586</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6691,6 +7116,9 @@
       <c r="N142" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O142" t="n">
+        <v>11.03793999763699</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6735,6 +7163,9 @@
       <c r="N143" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O143" t="n">
+        <v>8.665111332096586</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6779,6 +7210,9 @@
       <c r="N144" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O144" t="n">
+        <v>14.59718299594759</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6823,6 +7257,9 @@
       <c r="N145" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O145" t="n">
+        <v>11.03793999763699</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6867,6 +7304,9 @@
       <c r="N146" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O146" t="n">
+        <v>8.665111332096586</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6911,6 +7351,9 @@
       <c r="N147" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O147" t="n">
+        <v>14.59718299594759</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -6955,6 +7398,9 @@
       <c r="N148" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O148" t="n">
+        <v>11.03793999763699</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -6999,6 +7445,9 @@
       <c r="N149" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O149" t="n">
+        <v>8.665111332096586</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -7043,6 +7492,9 @@
       <c r="N150" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O150" t="n">
+        <v>20.52925465979861</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -7087,6 +7539,9 @@
       <c r="N151" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O151" t="n">
+        <v>14.59718299594759</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -7131,6 +7586,9 @@
       <c r="N152" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O152" t="n">
+        <v>11.03793999763699</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -7175,6 +7633,9 @@
       <c r="N153" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O153" t="n">
+        <v>8.665111332096586</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -7219,6 +7680,9 @@
       <c r="N154" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O154" t="n">
+        <v>9.065775279212854</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -7263,6 +7727,9 @@
       <c r="N155" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O155" t="n">
+        <v>11.03793999763699</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -7307,6 +7774,9 @@
       <c r="N156" t="n">
         <v>3284.215906797902</v>
       </c>
+      <c r="O156" t="n">
+        <v>8.665111332096586</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -7351,6 +7821,9 @@
       <c r="N157" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O157" t="n">
+        <v>9.011715785380449</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -7395,6 +7868,9 @@
       <c r="N158" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O158" t="n">
+        <v>11.47945759754247</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -7439,6 +7915,9 @@
       <c r="N159" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O159" t="n">
+        <v>9.011715785380449</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -7483,6 +7962,9 @@
       <c r="N160" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O160" t="n">
+        <v>11.47945759754247</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -7527,6 +8009,9 @@
       <c r="N161" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O161" t="n">
+        <v>9.011715785380449</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -7571,6 +8056,9 @@
       <c r="N162" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O162" t="n">
+        <v>15.1810703157855</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -7615,6 +8103,9 @@
       <c r="N163" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O163" t="n">
+        <v>11.47945759754247</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -7659,6 +8150,9 @@
       <c r="N164" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O164" t="n">
+        <v>9.011715785380449</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -7703,6 +8197,9 @@
       <c r="N165" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O165" t="n">
+        <v>15.1810703157855</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -7747,6 +8244,9 @@
       <c r="N166" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O166" t="n">
+        <v>11.47945759754247</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -7791,6 +8291,9 @@
       <c r="N167" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O167" t="n">
+        <v>9.011715785380449</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -7835,6 +8338,9 @@
       <c r="N168" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O168" t="n">
+        <v>21.35042484619055</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -7879,6 +8385,9 @@
       <c r="N169" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O169" t="n">
+        <v>15.1810703157855</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -7923,6 +8432,9 @@
       <c r="N170" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O170" t="n">
+        <v>11.47945759754247</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -7967,6 +8479,9 @@
       <c r="N171" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O171" t="n">
+        <v>9.011715785380449</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -8011,6 +8526,9 @@
       <c r="N172" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O172" t="n">
+        <v>21.35042484619055</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -8055,6 +8573,9 @@
       <c r="N173" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O173" t="n">
+        <v>15.1810703157855</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -8099,6 +8620,9 @@
       <c r="N174" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O174" t="n">
+        <v>11.47945759754247</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -8143,6 +8667,9 @@
       <c r="N175" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O175" t="n">
+        <v>9.011715785380449</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -8187,6 +8714,9 @@
       <c r="N176" t="n">
         <v>3287.731784589987</v>
       </c>
+      <c r="O176" t="n">
+        <v>9.428406290381368</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -8231,6 +8761,9 @@
       <c r="N177" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O177" t="n">
+        <v>9.358320238664312</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -8275,6 +8808,9 @@
       <c r="N178" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O178" t="n">
+        <v>9.358320238664312</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -8319,6 +8855,9 @@
       <c r="N179" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O179" t="n">
+        <v>11.92097519744795</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -8363,6 +8902,9 @@
       <c r="N180" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O180" t="n">
+        <v>9.358320238664312</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -8407,6 +8949,9 @@
       <c r="N181" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O181" t="n">
+        <v>11.92097519744795</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -8451,6 +8996,9 @@
       <c r="N182" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O182" t="n">
+        <v>9.358320238664312</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -8495,6 +9043,9 @@
       <c r="N183" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O183" t="n">
+        <v>15.7649576356234</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -8539,6 +9090,9 @@
       <c r="N184" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O184" t="n">
+        <v>11.92097519744795</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -8583,6 +9137,9 @@
       <c r="N185" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O185" t="n">
+        <v>9.358320238664312</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -8627,6 +9184,9 @@
       <c r="N186" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O186" t="n">
+        <v>15.7649576356234</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -8671,6 +9231,9 @@
       <c r="N187" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O187" t="n">
+        <v>11.92097519744795</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -8715,6 +9278,9 @@
       <c r="N188" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O188" t="n">
+        <v>9.358320238664312</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -8759,6 +9325,9 @@
       <c r="N189" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O189" t="n">
+        <v>22.17159503258249</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -8803,6 +9372,9 @@
       <c r="N190" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O190" t="n">
+        <v>15.7649576356234</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -8847,6 +9419,9 @@
       <c r="N191" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O191" t="n">
+        <v>11.92097519744795</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -8891,6 +9466,9 @@
       <c r="N192" t="n">
         <v>3291.100890470622</v>
       </c>
+      <c r="O192" t="n">
+        <v>9.358320238664312</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -8935,6 +9513,9 @@
       <c r="N193" t="n">
         <v>3294.334216551842</v>
       </c>
+      <c r="O193" t="n">
+        <v>9.704924691948177</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -8979,6 +9560,9 @@
       <c r="N194" t="n">
         <v>3294.334216551842</v>
       </c>
+      <c r="O194" t="n">
+        <v>9.704924691948177</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -9023,6 +9607,9 @@
       <c r="N195" t="n">
         <v>3294.334216551842</v>
       </c>
+      <c r="O195" t="n">
+        <v>12.36249279735343</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -9067,6 +9654,9 @@
       <c r="N196" t="n">
         <v>3294.334216551842</v>
       </c>
+      <c r="O196" t="n">
+        <v>9.704924691948177</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -9111,6 +9701,9 @@
       <c r="N197" t="n">
         <v>3294.334216551842</v>
       </c>
+      <c r="O197" t="n">
+        <v>12.36249279735343</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -9155,6 +9748,9 @@
       <c r="N198" t="n">
         <v>3294.334216551842</v>
       </c>
+      <c r="O198" t="n">
+        <v>9.704924691948177</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -9199,6 +9795,9 @@
       <c r="N199" t="n">
         <v>3294.334216551842</v>
       </c>
+      <c r="O199" t="n">
+        <v>16.34884495546131</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -9243,6 +9842,9 @@
       <c r="N200" t="n">
         <v>3294.334216551842</v>
       </c>
+      <c r="O200" t="n">
+        <v>12.36249279735343</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -9287,6 +9889,9 @@
       <c r="N201" t="n">
         <v>3294.334216551842</v>
       </c>
+      <c r="O201" t="n">
+        <v>9.704924691948177</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -9331,6 +9936,9 @@
       <c r="N202" t="n">
         <v>3294.334216551842</v>
       </c>
+      <c r="O202" t="n">
+        <v>16.34884495546131</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -9375,6 +9983,9 @@
       <c r="N203" t="n">
         <v>3294.334216551842</v>
       </c>
+      <c r="O203" t="n">
+        <v>12.36249279735343</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -9419,6 +10030,9 @@
       <c r="N204" t="n">
         <v>3294.334216551842</v>
       </c>
+      <c r="O204" t="n">
+        <v>9.704924691948177</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -9463,6 +10077,9 @@
       <c r="N205" t="n">
         <v>3294.334216551842</v>
       </c>
+      <c r="O205" t="n">
+        <v>9.704924691948177</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -9507,6 +10124,9 @@
       <c r="N206" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O206" t="n">
+        <v>10.05152914523204</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -9551,6 +10171,9 @@
       <c r="N207" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O207" t="n">
+        <v>10.05152914523204</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -9595,6 +10218,9 @@
       <c r="N208" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O208" t="n">
+        <v>12.8040103972589</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -9639,6 +10265,9 @@
       <c r="N209" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O209" t="n">
+        <v>10.05152914523204</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -9683,6 +10312,9 @@
       <c r="N210" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O210" t="n">
+        <v>12.8040103972589</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -9727,6 +10359,9 @@
       <c r="N211" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O211" t="n">
+        <v>10.05152914523204</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -9771,6 +10406,9 @@
       <c r="N212" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O212" t="n">
+        <v>12.8040103972589</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -9815,6 +10453,9 @@
       <c r="N213" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O213" t="n">
+        <v>10.05152914523204</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -9859,6 +10500,9 @@
       <c r="N214" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O214" t="n">
+        <v>16.93273227529921</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -9903,6 +10547,9 @@
       <c r="N215" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O215" t="n">
+        <v>12.8040103972589</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -9947,6 +10594,9 @@
       <c r="N216" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O216" t="n">
+        <v>10.05152914523204</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -9991,6 +10641,9 @@
       <c r="N217" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O217" t="n">
+        <v>16.93273227529921</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -10035,6 +10688,9 @@
       <c r="N218" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O218" t="n">
+        <v>12.8040103972589</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -10079,6 +10735,9 @@
       <c r="N219" t="n">
         <v>3297.441582540153</v>
       </c>
+      <c r="O219" t="n">
+        <v>10.05152914523204</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -10123,6 +10782,9 @@
       <c r="N220" t="n">
         <v>3300.431795951522</v>
       </c>
+      <c r="O220" t="n">
+        <v>10.3981335985159</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -10167,6 +10829,9 @@
       <c r="N221" t="n">
         <v>3300.431795951522</v>
       </c>
+      <c r="O221" t="n">
+        <v>10.3981335985159</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -10211,6 +10876,9 @@
       <c r="N222" t="n">
         <v>3300.431795951522</v>
       </c>
+      <c r="O222" t="n">
+        <v>13.24552799716438</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -10255,6 +10923,9 @@
       <c r="N223" t="n">
         <v>3300.431795951522</v>
       </c>
+      <c r="O223" t="n">
+        <v>10.3981335985159</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -10299,6 +10970,9 @@
       <c r="N224" t="n">
         <v>3300.431795951522</v>
       </c>
+      <c r="O224" t="n">
+        <v>13.24552799716438</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -10343,6 +11017,9 @@
       <c r="N225" t="n">
         <v>3300.431795951522</v>
       </c>
+      <c r="O225" t="n">
+        <v>10.3981335985159</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -10387,6 +11064,9 @@
       <c r="N226" t="n">
         <v>3300.431795951522</v>
       </c>
+      <c r="O226" t="n">
+        <v>17.51661959513711</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -10431,6 +11111,9 @@
       <c r="N227" t="n">
         <v>3300.431795951522</v>
       </c>
+      <c r="O227" t="n">
+        <v>13.24552799716438</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -10475,6 +11158,9 @@
       <c r="N228" t="n">
         <v>3300.431795951522</v>
       </c>
+      <c r="O228" t="n">
+        <v>10.3981335985159</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -10519,6 +11205,9 @@
       <c r="N229" t="n">
         <v>3300.431795951522</v>
       </c>
+      <c r="O229" t="n">
+        <v>17.51661959513711</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -10563,6 +11252,9 @@
       <c r="N230" t="n">
         <v>3300.431795951522</v>
       </c>
+      <c r="O230" t="n">
+        <v>13.24552799716438</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -10607,6 +11299,9 @@
       <c r="N231" t="n">
         <v>3300.431795951522</v>
       </c>
+      <c r="O231" t="n">
+        <v>10.3981335985159</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -10651,6 +11346,9 @@
       <c r="N232" t="n">
         <v>3303.312777946501</v>
       </c>
+      <c r="O232" t="n">
+        <v>10.74473805179976</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -10695,6 +11393,9 @@
       <c r="N233" t="n">
         <v>3303.312777946501</v>
       </c>
+      <c r="O233" t="n">
+        <v>10.74473805179976</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -10739,6 +11440,9 @@
       <c r="N234" t="n">
         <v>3303.312777946501</v>
       </c>
+      <c r="O234" t="n">
+        <v>13.68704559706986</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -10783,6 +11487,9 @@
       <c r="N235" t="n">
         <v>3303.312777946501</v>
       </c>
+      <c r="O235" t="n">
+        <v>10.74473805179976</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -10827,6 +11534,9 @@
       <c r="N236" t="n">
         <v>3303.312777946501</v>
       </c>
+      <c r="O236" t="n">
+        <v>13.68704559706986</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -10871,6 +11581,9 @@
       <c r="N237" t="n">
         <v>3303.312777946501</v>
       </c>
+      <c r="O237" t="n">
+        <v>10.74473805179976</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -10915,6 +11628,9 @@
       <c r="N238" t="n">
         <v>3303.312777946501</v>
       </c>
+      <c r="O238" t="n">
+        <v>18.10050691497502</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -10959,6 +11675,9 @@
       <c r="N239" t="n">
         <v>3303.312777946501</v>
       </c>
+      <c r="O239" t="n">
+        <v>13.68704559706986</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -11003,6 +11722,9 @@
       <c r="N240" t="n">
         <v>3303.312777946501</v>
       </c>
+      <c r="O240" t="n">
+        <v>10.74473805179976</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -11047,6 +11769,9 @@
       <c r="N241" t="n">
         <v>3306.091707362888</v>
       </c>
+      <c r="O241" t="n">
+        <v>11.09134250508363</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -11091,6 +11816,9 @@
       <c r="N242" t="n">
         <v>3306.091707362888</v>
       </c>
+      <c r="O242" t="n">
+        <v>11.09134250508363</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -11135,6 +11863,9 @@
       <c r="N243" t="n">
         <v>3306.091707362888</v>
       </c>
+      <c r="O243" t="n">
+        <v>14.12856319697534</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -11179,6 +11910,9 @@
       <c r="N244" t="n">
         <v>3306.091707362888</v>
       </c>
+      <c r="O244" t="n">
+        <v>11.09134250508363</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -11223,6 +11957,9 @@
       <c r="N245" t="n">
         <v>3306.091707362888</v>
       </c>
+      <c r="O245" t="n">
+        <v>14.12856319697534</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -11267,6 +12004,9 @@
       <c r="N246" t="n">
         <v>3306.091707362888</v>
       </c>
+      <c r="O246" t="n">
+        <v>11.09134250508363</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -11311,6 +12051,9 @@
       <c r="N247" t="n">
         <v>3306.091707362888</v>
       </c>
+      <c r="O247" t="n">
+        <v>14.12856319697534</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -11355,6 +12098,9 @@
       <c r="N248" t="n">
         <v>3306.091707362888</v>
       </c>
+      <c r="O248" t="n">
+        <v>11.09134250508363</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -11399,6 +12145,9 @@
       <c r="N249" t="n">
         <v>3306.091707362888</v>
       </c>
+      <c r="O249" t="n">
+        <v>11.09134250508363</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -11443,6 +12192,9 @@
       <c r="N250" t="n">
         <v>3308.775067964652</v>
       </c>
+      <c r="O250" t="n">
+        <v>11.43794695836749</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -11487,6 +12239,9 @@
       <c r="N251" t="n">
         <v>3308.775067964652</v>
       </c>
+      <c r="O251" t="n">
+        <v>11.43794695836749</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -11531,6 +12286,9 @@
       <c r="N252" t="n">
         <v>3308.775067964652</v>
       </c>
+      <c r="O252" t="n">
+        <v>14.57008079688082</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -11575,6 +12333,9 @@
       <c r="N253" t="n">
         <v>3308.775067964652</v>
       </c>
+      <c r="O253" t="n">
+        <v>11.43794695836749</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -11619,6 +12380,9 @@
       <c r="N254" t="n">
         <v>3308.775067964652</v>
       </c>
+      <c r="O254" t="n">
+        <v>14.57008079688082</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -11663,6 +12427,9 @@
       <c r="N255" t="n">
         <v>3308.775067964652</v>
       </c>
+      <c r="O255" t="n">
+        <v>11.43794695836749</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -11707,6 +12474,9 @@
       <c r="N256" t="n">
         <v>3308.775067964652</v>
       </c>
+      <c r="O256" t="n">
+        <v>14.57008079688082</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -11751,6 +12521,9 @@
       <c r="N257" t="n">
         <v>3308.775067964652</v>
       </c>
+      <c r="O257" t="n">
+        <v>11.43794695836749</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -11795,6 +12568,9 @@
       <c r="N258" t="n">
         <v>3311.368761383796</v>
       </c>
+      <c r="O258" t="n">
+        <v>11.78455141165136</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -11839,6 +12615,9 @@
       <c r="N259" t="n">
         <v>3311.368761383796</v>
       </c>
+      <c r="O259" t="n">
+        <v>11.78455141165136</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -11883,6 +12662,9 @@
       <c r="N260" t="n">
         <v>3311.368761383796</v>
       </c>
+      <c r="O260" t="n">
+        <v>11.78455141165136</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -11927,6 +12709,9 @@
       <c r="N261" t="n">
         <v>3311.368761383796</v>
       </c>
+      <c r="O261" t="n">
+        <v>15.0115983967863</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -11971,6 +12756,9 @@
       <c r="N262" t="n">
         <v>3311.368761383796</v>
       </c>
+      <c r="O262" t="n">
+        <v>11.78455141165136</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -12015,6 +12803,9 @@
       <c r="N263" t="n">
         <v>3311.368761383796</v>
       </c>
+      <c r="O263" t="n">
+        <v>15.0115983967863</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -12059,6 +12850,9 @@
       <c r="N264" t="n">
         <v>3311.368761383796</v>
       </c>
+      <c r="O264" t="n">
+        <v>11.78455141165136</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -12103,6 +12897,9 @@
       <c r="N265" t="n">
         <v>3313.878168020069</v>
       </c>
+      <c r="O265" t="n">
+        <v>12.13115586493522</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -12147,6 +12944,9 @@
       <c r="N266" t="n">
         <v>3313.878168020069</v>
       </c>
+      <c r="O266" t="n">
+        <v>12.13115586493522</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -12191,6 +12991,9 @@
       <c r="N267" t="n">
         <v>3313.878168020069</v>
       </c>
+      <c r="O267" t="n">
+        <v>12.13115586493522</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -12235,6 +13038,9 @@
       <c r="N268" t="n">
         <v>3313.878168020069</v>
       </c>
+      <c r="O268" t="n">
+        <v>15.45311599669178</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -12279,6 +13085,9 @@
       <c r="N269" t="n">
         <v>3313.878168020069</v>
       </c>
+      <c r="O269" t="n">
+        <v>12.13115586493522</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -12323,6 +13132,9 @@
       <c r="N270" t="n">
         <v>3316.308206285463</v>
       </c>
+      <c r="O270" t="n">
+        <v>12.47776031821908</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -12367,6 +13179,9 @@
       <c r="N271" t="n">
         <v>3316.308206285463</v>
       </c>
+      <c r="O271" t="n">
+        <v>12.47776031821908</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -12411,6 +13226,9 @@
       <c r="N272" t="n">
         <v>3316.308206285463</v>
       </c>
+      <c r="O272" t="n">
+        <v>15.89463359659726</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -12455,6 +13273,9 @@
       <c r="N273" t="n">
         <v>3316.308206285463</v>
       </c>
+      <c r="O273" t="n">
+        <v>12.47776031821908</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -12499,6 +13320,9 @@
       <c r="N274" t="n">
         <v>3318.663377273083</v>
       </c>
+      <c r="O274" t="n">
+        <v>12.82436477150294</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -12543,6 +13367,9 @@
       <c r="N275" t="n">
         <v>3318.663377273083</v>
       </c>
+      <c r="O275" t="n">
+        <v>12.82436477150294</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -12587,6 +13414,9 @@
       <c r="N276" t="n">
         <v>3318.663377273083</v>
       </c>
+      <c r="O276" t="n">
+        <v>12.82436477150294</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -12631,6 +13461,9 @@
       <c r="N277" t="n">
         <v>3318.663377273083</v>
       </c>
+      <c r="O277" t="n">
+        <v>16.33615119650274</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -12675,6 +13508,9 @@
       <c r="N278" t="n">
         <v>3318.663377273083</v>
       </c>
+      <c r="O278" t="n">
+        <v>12.82436477150294</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -12719,6 +13555,9 @@
       <c r="N279" t="n">
         <v>3320.947834844403</v>
       </c>
+      <c r="O279" t="n">
+        <v>13.17096922478681</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -12763,6 +13602,9 @@
       <c r="N280" t="n">
         <v>3320.947834844403</v>
       </c>
+      <c r="O280" t="n">
+        <v>13.17096922478681</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -12807,6 +13649,9 @@
       <c r="N281" t="n">
         <v>3320.947834844403</v>
       </c>
+      <c r="O281" t="n">
+        <v>13.17096922478681</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -12851,6 +13696,9 @@
       <c r="N282" t="n">
         <v>3323.165385011158</v>
       </c>
+      <c r="O282" t="n">
+        <v>13.51757367807067</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -12895,6 +13743,9 @@
       <c r="N283" t="n">
         <v>3323.165385011158</v>
       </c>
+      <c r="O283" t="n">
+        <v>13.51757367807067</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -12939,6 +13790,9 @@
       <c r="N284" t="n">
         <v>3323.165385011158</v>
       </c>
+      <c r="O284" t="n">
+        <v>13.51757367807067</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -12983,6 +13837,9 @@
       <c r="N285" t="n">
         <v>3325.319545748981</v>
       </c>
+      <c r="O285" t="n">
+        <v>13.86417813135454</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -13027,6 +13884,9 @@
       <c r="N286" t="n">
         <v>3325.319545748981</v>
       </c>
+      <c r="O286" t="n">
+        <v>13.86417813135454</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -13071,6 +13931,9 @@
       <c r="N287" t="n">
         <v>3327.413569771421</v>
       </c>
+      <c r="O287" t="n">
+        <v>14.2107825846384</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -13115,6 +13978,9 @@
       <c r="N288" t="n">
         <v>3329.450470382038</v>
       </c>
+      <c r="O288" t="n">
+        <v>14.55738703792226</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -13159,6 +14025,9 @@
       <c r="N289" t="n">
         <v>3329.450470382038</v>
       </c>
+      <c r="O289" t="n">
+        <v>14.55738703792226</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -13203,6 +14072,9 @@
       <c r="N290" t="n">
         <v>3331.433044132794</v>
       </c>
+      <c r="O290" t="n">
+        <v>14.90399149120613</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -13246,6 +14118,9 @@
       </c>
       <c r="N291" t="n">
         <v>3333.36388587817</v>
+      </c>
+      <c r="O291" t="n">
+        <v>15.25059594448999</v>
       </c>
     </row>
   </sheetData>
